--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N38_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N38_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>39.00286628964698</v>
+        <v>6.337965772067634</v>
       </c>
       <c r="D2" t="n">
-        <v>16.76483238071131</v>
+        <v>2.724285261865588</v>
       </c>
       <c r="E2" t="n">
-        <v>15.25163674843888</v>
+        <v>2.478390971621318</v>
       </c>
       <c r="F2" t="n">
-        <v>13.48642606541371</v>
+        <v>2.191544235629729</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>51.97698222735258</v>
+        <v>8.446259611944795</v>
       </c>
       <c r="D3" t="n">
-        <v>49.83833758016497</v>
+        <v>8.098729856776808</v>
       </c>
       <c r="E3" t="n">
-        <v>15.25163674843888</v>
+        <v>2.478390971621318</v>
       </c>
       <c r="F3" t="n">
-        <v>13.48642606541371</v>
+        <v>2.191544235629729</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>71.98490393501771</v>
+        <v>11.69754688944038</v>
       </c>
       <c r="D4" t="n">
-        <v>23.61131637138675</v>
+        <v>3.836838910350346</v>
       </c>
       <c r="E4" t="n">
-        <v>15.25163674843888</v>
+        <v>2.478390971621318</v>
       </c>
       <c r="F4" t="n">
-        <v>13.48642606541371</v>
+        <v>2.191544235629729</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>78.22126783479126</v>
+        <v>12.71095602315358</v>
       </c>
       <c r="D5" t="n">
-        <v>16.45223629089777</v>
+        <v>2.673488397270888</v>
       </c>
       <c r="E5" t="n">
-        <v>15.25163674843888</v>
+        <v>2.478390971621318</v>
       </c>
       <c r="F5" t="n">
-        <v>13.48642606541371</v>
+        <v>2.191544235629729</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>75.40084287961247</v>
+        <v>12.25263696793703</v>
       </c>
       <c r="D6" t="n">
-        <v>40.84307087032705</v>
+        <v>6.636999016428146</v>
       </c>
       <c r="E6" t="n">
-        <v>15.25163674843888</v>
+        <v>2.478390971621318</v>
       </c>
       <c r="F6" t="n">
-        <v>13.48642606541371</v>
+        <v>2.191544235629729</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
